--- a/src/Desktop/resources/import-templates/personal-records.xlsx
+++ b/src/Desktop/resources/import-templates/personal-records.xlsx
@@ -250,7 +250,7 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">在导入窗口选择原记录的时区（中国时间为 +08:00）。填写实际游戏时间时须有完整日期和时分；未知时间留空。确认本人导随及通关结果后，缺少进本或结束时间仅显示为待补充，仍计入完成次数与成就；未知耗时不计入平均耗时。</t>
+          <t xml:space="preserve">在导入窗口选择原记录的时区（中国时间为 +08:00）。实际游戏时刻须有完整日期和时分；未知时间留空。Excel/CSV/粘贴表格的开始时间仅有完整日期时，日期保留为记录日期，不补成午夜；如与已有记录日期冲突，须核对并修正，不能覆盖原日期。结束时间不能只填日期。确认本人导随及通关结果后，缺少进本或结束时间仅显示为待补充，仍计入完成次数与成就；未知耗时不计入平均耗时。</t>
         </is>
       </c>
     </row>
@@ -286,7 +286,7 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">可填写带时区的时间，例如 2026-10-10T20:00:00+08:00（中国时间）或 2026-10-10T12:00:00Z（UTC）。没有时区的本地时间按导入窗口选择的来源时区处理。</t>
+          <t xml:space="preserve">实际进本/结束时刻必须包含日期和时分，不能只填日期；只记得日期时填写 source_recorded_at，实际时刻留 null。可填写带时区的时间，例如 2026-10-10T20:00:00+08:00（中国时间）或 2026-10-10T12:00:00Z（UTC）。没有时区的本地时间按导入窗口选择的来源时区处理。</t>
         </is>
       </c>
     </row>
@@ -370,7 +370,7 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">实际进本时间。填写完整日期和时分，例如 2026-10-10 20:00；未知时留空。</t>
+          <t xml:space="preserve">实际进本时间。已知时填写完整日期和时分，例如 2026-10-10 20:00。Excel/CSV/粘贴表格仅有日期（2026-10-10、2026/10/10 或 2026.10.10）时保留为记录日期，实际进本时刻仍为空；未知时留空。</t>
         </is>
       </c>
     </row>
@@ -382,7 +382,7 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">实际结束时间。格式同开始时间，不能早于开始时间；未知时留空。</t>
+          <t xml:space="preserve">实际结束时间。须填写完整日期和时分，不能只填日期，也不能早于开始时间；未知时留空。</t>
         </is>
       </c>
     </row>

--- a/src/Desktop/resources/import-templates/personal-records.xlsx
+++ b/src/Desktop/resources/import-templates/personal-records.xlsx
@@ -80,6 +80,7 @@
     <col min="8" max="8" width="16" customWidth="1" style="2"/>
     <col min="9" max="9" width="25" customWidth="1" style="2"/>
     <col min="10" max="10" width="45" customWidth="1" style="2"/>
+    <col min="11" max="11" width="20" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -133,6 +134,11 @@
           <t xml:space="preserve">备注</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">进入方式</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" t="inlineStr" s="2">
@@ -185,9 +191,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请使用支持的值" error="请选择列表中的值" sqref="E2:E5001">
       <formula1>"通关,未知,离开,放弃,取消,中断,掉线"</formula1>
@@ -458,6 +469,18 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="100" customHeight="1">
+      <c r="A22" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">进入方式 / joined_in_progress</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正常或开局进入表示从开局进入（false）；中途或中途加入表示中途进入（true）。未知时 Excel 留空，JSON 保留 null；不会自动按正常进入统计。JSON 也可填写布尔值 false 或 true。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>